--- a/Projects/Javonte-Green.xlsx
+++ b/Projects/Javonte-Green.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Documents/GitHub/basketball-analytics/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B97AA1F0-8ED7-FD4E-BA69-19F8923B0562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A09424D-D7D9-D049-9FE8-1A030BC432B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1400" windowWidth="27640" windowHeight="16680" activeTab="7" xr2:uid="{91DDF0CC-1112-E742-B0ED-4CCF8B231B63}"/>
+    <workbookView xWindow="1500" yWindow="1400" windowWidth="27640" windowHeight="16680" activeTab="8" xr2:uid="{91DDF0CC-1112-E742-B0ED-4CCF8B231B63}"/>
   </bookViews>
   <sheets>
     <sheet name="Per Game" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="Advanced Shooting" sheetId="6" r:id="rId6"/>
     <sheet name="Play-by-Play" sheetId="7" r:id="rId7"/>
     <sheet name="Shooting" sheetId="8" r:id="rId8"/>
+    <sheet name="Resources" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="127">
   <si>
     <t>Season</t>
   </si>
@@ -418,6 +419,12 @@
   </si>
   <si>
     <t>Md._1/2-Court</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>https://www.basketball-reference.com/players/g/greenja02.html</t>
   </si>
 </sst>
 </file>
@@ -10009,4 +10016,24 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DBC98BD-6F94-A74F-9C4B-B4F1AAE18A65}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Projects/Javonte-Green.xlsx
+++ b/Projects/Javonte-Green.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Documents/GitHub/basketball-analytics/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A09424D-D7D9-D049-9FE8-1A030BC432B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA800BA0-0514-4F42-B45D-7E3673A89273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1400" windowWidth="27640" windowHeight="16680" activeTab="8" xr2:uid="{91DDF0CC-1112-E742-B0ED-4CCF8B231B63}"/>
+    <workbookView xWindow="1500" yWindow="1400" windowWidth="27640" windowHeight="16680" activeTab="5" xr2:uid="{91DDF0CC-1112-E742-B0ED-4CCF8B231B63}"/>
   </bookViews>
   <sheets>
     <sheet name="Per Game" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Per 36" sheetId="3" r:id="rId3"/>
     <sheet name="Per 100 Poss" sheetId="4" r:id="rId4"/>
     <sheet name="Advanced" sheetId="5" r:id="rId5"/>
-    <sheet name="Advanced Shooting" sheetId="6" r:id="rId6"/>
+    <sheet name="Adjusted Shooting" sheetId="6" r:id="rId6"/>
     <sheet name="Play-by-Play" sheetId="7" r:id="rId7"/>
     <sheet name="Shooting" sheetId="8" r:id="rId8"/>
     <sheet name="Resources" sheetId="9" r:id="rId9"/>
